--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig11_pls_peer_selection_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig11_pls_peer_selection_data.xlsx
@@ -445,7 +445,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,6 +1298,21 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>selected_peer_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>redundancy_status</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>topology_contract</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>selection_rule</t>
         </is>
       </c>
@@ -1315,19 +1330,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DO_1_3;DO_2_2;DO_2_3;DO_2_4</t>
+          <t>DO_1_3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DO_1_2;DO_2_1;DO_2_4</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>DO_2_4</t>
-        </is>
-      </c>
+          <t>DO_1_2;DO_2_1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>0.4529522521903347</v>
       </c>
@@ -1335,20 +1346,33 @@
         <v>0.5538093389402775</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4424993193809978</v>
+        <v>0.4529522521903347</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5485682232976706</v>
+        <v>0.5538093389402775</v>
       </c>
       <c r="J2" t="n">
-        <v>2.307733929744207</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1363,11 +1387,7 @@
           <t>DO_1_1;DO_1_3;DO_2_2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DO_2_1;DO_2_3;DO_2_4</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>DO_1_1;DO_1_3;DO_2_2</t>
@@ -1392,9 +1412,22 @@
       <c r="K3" t="n">
         <v>3</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1444,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DO_1_1;DO_2_1;DO_2_2;DO_2_4</t>
+          <t>DO_1_1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1438,9 +1471,22 @@
       <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1503,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DO_1_1;DO_1_2;DO_2_1;DO_2_2;DO_2_3</t>
+          <t>DO_1_2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1484,9 +1530,22 @@
       <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1562,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DO_1_2;DO_1_3;DO_2_3;DO_2_4</t>
+          <t>DO_2_3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1530,9 +1589,22 @@
       <c r="K6" t="n">
         <v>3</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1621,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DO_1_1;DO_1_3;DO_2_4</t>
+          <t>DO_2_4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1576,9 +1648,22 @@
       <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1680,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DO_1_1;DO_1_2;DO_2_1</t>
+          <t>DO_2_1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1622,9 +1707,22 @@
       <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1636,41 +1734,58 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DO_1_1;DO_1_2</t>
+          <t>DO_2_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DO_1_3;DO_2_1;DO_2_2;DO_2_3</t>
+          <t>DO_2_2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DO_1_1;DO_1_2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>DO_2_3;DO_2_2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>1.035829134754189</v>
+        <v>0.9754254903453224</v>
       </c>
       <c r="G9" t="n">
-        <v>1.693174811018386</v>
+        <v>1.80142554319854</v>
       </c>
       <c r="H9" t="n">
-        <v>1.035829134754189</v>
+        <v>0.8505087141750978</v>
       </c>
       <c r="I9" t="n">
-        <v>1.693174811018386</v>
+        <v>1.835155804695652</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>12.80638833069673</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1802,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ORP_1_3;ORP_2_2;ORP_2_3</t>
+          <t>ORP_1_3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1714,9 +1829,22 @@
       <c r="K10" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1731,21 +1859,13 @@
           <t>ORP_1_1;ORP_1_3;ORP_2_2</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ORP_2_1;ORP_2_3</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ORP_1_1;ORP_1_3;ORP_2_2;ORP_2_1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ORP_2_1</t>
-        </is>
-      </c>
+          <t>ORP_1_1;ORP_1_3;ORP_2_2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
         <v>0.5190631071704501</v>
       </c>
@@ -1753,20 +1873,33 @@
         <v>0.8683919385115014</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4924382329981556</v>
+        <v>0.5190631071704501</v>
       </c>
       <c r="I11" t="n">
-        <v>0.888522989971177</v>
+        <v>0.8683919385115014</v>
       </c>
       <c r="J11" t="n">
-        <v>5.129409854889079</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1916,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ORP_1_1;ORP_2_1;ORP_2_2</t>
+          <t>ORP_1_1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1810,9 +1943,22 @@
       <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1829,19 +1975,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ORP_1_2;ORP_1_3;ORP_2_3</t>
+          <t>ORP_2_3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ORP_1_1;ORP_2_2;ORP_1_2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ORP_1_2</t>
-        </is>
-      </c>
+          <t>ORP_1_1;ORP_2_2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>0.4611344430681601</v>
       </c>
@@ -1849,20 +1991,33 @@
         <v>0.7167660015381367</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4390872711343277</v>
+        <v>0.4611344430681601</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7397015754965461</v>
+        <v>0.7167660015381367</v>
       </c>
       <c r="J13" t="n">
-        <v>4.78107247577116</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1877,11 +2032,7 @@
           <t>ORP_1_2;ORP_2_1;ORP_2_3</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ORP_1_1;ORP_1_3</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>ORP_1_2;ORP_2_1;ORP_2_3</t>
@@ -1906,9 +2057,22 @@
       <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
@@ -1925,7 +2089,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ORP_1_1;ORP_1_2;ORP_2_1</t>
+          <t>ORP_2_1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1952,9 +2116,22 @@
       <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>same-analyte core + blocked-CV forward selection</t>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>multi_peer</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>same-analyte adjacent/twin core; same-pool second-order CV expansion</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>topology core + same-pool second-order blocked-CV expansion</t>
         </is>
       </c>
     </row>
